--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484671_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484671_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7831</v>
+        <v>1.4842</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4291</v>
+        <v>4.3407</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.646</v>
+        <v>-2.8565</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7936</v>
+        <v>0.1419</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0408</v>
+        <v>2.8794</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2472</v>
+        <v>-2.7375</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0075</v>
+        <v>2.751</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9658</v>
+        <v>3.9815</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0417</v>
+        <v>-1.2305</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2139</v>
+        <v>-2.6091</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.925</v>
+        <v>-1.1021</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2888</v>
+        <v>-1.5069</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2828</v>
+        <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4555</v>
+        <v>-0.2521</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9035</v>
+        <v>-0.3499</v>
       </c>
       <c r="U2" t="n">
-        <v>0.552</v>
+        <v>0.0978</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
       <c r="W2" t="n">
-        <v>1.267</v>
+        <v>2.8559</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.267</v>
+        <v>-2.5444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>L. JURADO TRAVER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4594</v>
+        <v>1.1118</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3407</v>
+        <v>1.0877</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8813</v>
+        <v>0.0241</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1419</v>
+        <v>-0.5291</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8794</v>
+        <v>-0.356</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.7375</v>
+        <v>-0.1731</v>
       </c>
       <c r="J3" t="n">
-        <v>2.751</v>
+        <v>1.1993</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9815</v>
+        <v>1.1796</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2305</v>
+        <v>0.0197</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6091</v>
+        <v>-1.7284</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1021</v>
+        <v>-1.5356</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5069</v>
+        <v>-0.1928</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2828</v>
+        <v>2.3823</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1991</v>
+        <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2768</v>
+        <v>-0.3614</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3499</v>
+        <v>-0.1116</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0731</v>
+        <v>-0.2498</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3115</v>
+        <v>-0.3801</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.5444</v>
+        <v>-0.3801</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. JURADO TRAVER</t>
+          <t>E. NAVARRO VALDÉS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8888</v>
+        <v>0.6251</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0877</v>
+        <v>0.6251</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1989</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5291</v>
+        <v>0.6251</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.356</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1731</v>
+        <v>0.6251</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1993</v>
+        <v>0.6251</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1796</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0197</v>
+        <v>0.6251</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7284</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5356</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1928</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5844</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1116</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4728</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3801</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDÉS</t>
+          <t>L. SALVADOR MONTAÑES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6251</v>
+        <v>0.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6251</v>
+        <v>0.3251</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6251</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6251</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6251</v>
+        <v>0.3251</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6251</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>E. CIRCUNS RIVERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4461</v>
+        <v>0.0441</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6885</v>
+        <v>2.318</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2424</v>
+        <v>-2.2739</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.384</v>
+        <v>-1.9878</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0459</v>
+        <v>0.8938</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4298</v>
+        <v>-2.8816</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0815</v>
+        <v>0.8776</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3159</v>
+        <v>2.1241</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.3974</v>
+        <v>-1.2464</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3024</v>
+        <v>-2.8655</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.27</v>
+        <v>-1.2303</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0324</v>
+        <v>-1.6351</v>
       </c>
       <c r="P6" t="n">
         <v>1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3823</v>
+        <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>0.744</v>
+        <v>-0.0094</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4193</v>
+        <v>-0.1485</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3247</v>
+        <v>0.1391</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3801</v>
+        <v>0.5753</v>
       </c>
       <c r="W6" t="n">
-        <v>1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6471</v>
+        <v>-1.0136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTAÑES</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3251</v>
+        <v>-0.0031</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3251</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.8938</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3251</v>
+        <v>0.7936</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3251</v>
+        <v>1.0408</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.2472</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3251</v>
+        <v>2.0075</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3251</v>
+        <v>1.9658</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.2139</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.925</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.2888</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.6693</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.3043</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. CIRCUNS RIVERA</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6755</v>
+        <v>-0.0872</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5488</v>
+        <v>0.3039</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2243</v>
+        <v>-0.3911</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9878</v>
+        <v>-1.384</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8938</v>
+        <v>1.0459</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8816</v>
+        <v>-2.4298</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8776</v>
+        <v>-0.0815</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1241</v>
+        <v>2.3159</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2464</v>
+        <v>-2.3974</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8655</v>
+        <v>-1.3024</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2303</v>
+        <v>-1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6351</v>
+        <v>-0.0324</v>
       </c>
       <c r="P8" t="n">
         <v>1.4661</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4661</v>
+        <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7291</v>
+        <v>0.2108</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0.0347</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1887</v>
+        <v>0.1761</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5753</v>
+        <v>-0.3801</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5889</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0136</v>
+        <v>-1.6471</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>R. ROMAN MORA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4466</v>
+        <v>-0.4862</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9119</v>
+        <v>-0.4772</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5347</v>
+        <v>-0.0091</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1832</v>
+        <v>3.1738</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6829</v>
+        <v>4.1453</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4998</v>
+        <v>-0.9715</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1576</v>
+        <v>4.9343</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7153</v>
+        <v>5.4245</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5577</v>
+        <v>-0.4902</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3407</v>
+        <v>-1.7605</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3982</v>
+        <v>-1.2792</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0575</v>
+        <v>-0.4813</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-3.2986</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>-5.4977</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9415</v>
+        <v>-0.2928</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8258</v>
+        <v>-0.2356</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1157</v>
+        <v>-0.0572</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9109</v>
+        <v>-0.3905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. ROMAN MORA</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.525</v>
+        <v>-0.6744</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3425</v>
+        <v>-0.2388</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1825</v>
+        <v>-0.4356</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1738</v>
+        <v>-0.1832</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1453</v>
+        <v>-0.6829</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9715</v>
+        <v>0.4998</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9343</v>
+        <v>0.1576</v>
       </c>
       <c r="K10" t="n">
-        <v>5.4245</v>
+        <v>0.7153</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4902</v>
+        <v>-0.5577</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7605</v>
+        <v>-0.3407</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2792</v>
+        <v>-1.3982</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4813</v>
+        <v>1.0575</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.2986</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.4977</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1991</v>
+        <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3316</v>
+        <v>-0.1693</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.101</v>
+        <v>-0.1527</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2306</v>
+        <v>-0.0166</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.3219</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3905</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.072</v>
+        <v>-2.0472</v>
       </c>
       <c r="E11" t="n">
         <v>-0.9163</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1557</v>
+        <v>-1.131</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8683</v>
@@ -1312,13 +1312,13 @@
         <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3869</v>
+        <v>-0.3622</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1117</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5258</v>
+        <v>-3.0561</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9086</v>
+        <v>-1.3894</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6171</v>
+        <v>-1.6667</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0546</v>
@@ -1390,13 +1390,13 @@
         <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6812</v>
+        <v>0.1508</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6946</v>
+        <v>0.2138</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0134</v>
+        <v>-0.063</v>
       </c>
       <c r="V12" t="n">
         <v>-0.702</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0803</v>
+        <v>-5.0337</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9891</v>
+        <v>-3.8929</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0913</v>
+        <v>-1.1408</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6099</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2713</v>
+        <v>-0.2247</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3673</v>
+        <v>-0.2711</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0959</v>
+        <v>0.0464</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6335</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.797600000000001</v>
+        <v>-7.797599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9766</v>
+        <v>2.976500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.7742</v>
+        <v>-10.7744</v>
       </c>
       <c r="G14" t="n">
         <v>-5.5574</v>
@@ -1516,7 +1516,7 @@
         <v>4.380899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.9382</v>
+        <v>-9.938199999999998</v>
       </c>
       <c r="J14" t="n">
         <v>11.5114</v>
@@ -1546,10 +1546,10 @@
         <v>16.4932</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6409000000000001</v>
+        <v>-0.641</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9313</v>
+        <v>-0.9312</v>
       </c>
       <c r="U14" t="n">
         <v>0.2902</v>
@@ -1558,7 +1558,7 @@
         <v>-1.5994</v>
       </c>
       <c r="W14" t="n">
-        <v>8.889599999999998</v>
+        <v>8.8896</v>
       </c>
       <c r="X14" t="n">
         <v>-10.4891</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>M. PERAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2308</v>
+        <v>5.3398</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2382</v>
+        <v>6.1359</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9926</v>
+        <v>-0.796</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0591</v>
+        <v>1.4869</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.5539</v>
+        <v>0.4224</v>
       </c>
       <c r="I15" t="n">
-        <v>5.613</v>
+        <v>1.0644</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3324</v>
+        <v>3.6668</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3192</v>
+        <v>3.5638</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6516</v>
+        <v>0.103</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2733</v>
+        <v>-2.1799</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.2347</v>
+        <v>-3.1413</v>
       </c>
       <c r="O15" t="n">
         <v>0.9614</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2828</v>
+        <v>2.1991</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8443</v>
+        <v>-0.8801</v>
       </c>
       <c r="T15" t="n">
-        <v>0.822</v>
+        <v>-0.3869</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0223</v>
+        <v>-0.4932</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9554</v>
+        <v>2.5339</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9554</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PERAL</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.046</v>
+        <v>4.0418</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3666</v>
+        <v>3.5651</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3206</v>
+        <v>0.4767</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4869</v>
+        <v>3.0591</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4224</v>
+        <v>-2.5539</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0644</v>
+        <v>5.613</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6668</v>
+        <v>4.3324</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5638</v>
+        <v>-0.3192</v>
       </c>
       <c r="L16" t="n">
-        <v>0.103</v>
+        <v>4.6516</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1799</v>
+        <v>-1.2733</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.1413</v>
+        <v>-2.2347</v>
       </c>
       <c r="O16" t="n">
         <v>0.9614</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1991</v>
+        <v>1.2828</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
         <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1739</v>
+        <v>0.6553</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1561</v>
+        <v>0.149</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0178</v>
+        <v>0.5064</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5339</v>
+        <v>-0.9554</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3219</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7996</v>
+        <v>2.6028</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6596</v>
+        <v>2.7558</v>
       </c>
       <c r="F18" t="n">
-        <v>0.14</v>
+        <v>-0.1529</v>
       </c>
       <c r="G18" t="n">
         <v>0.3436</v>
@@ -1858,13 +1858,13 @@
         <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6001</v>
+        <v>0.4033</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2361</v>
+        <v>0.3322</v>
       </c>
       <c r="U18" t="n">
-        <v>0.364</v>
+        <v>0.0711</v>
       </c>
       <c r="V18" t="n">
         <v>2.2224</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9986</v>
+        <v>1.9719</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1923</v>
+        <v>0.3847</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1909</v>
+        <v>1.5873</v>
       </c>
       <c r="G19" t="n">
         <v>1.5731</v>
@@ -1936,13 +1936,13 @@
         <v>2.3823</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5977</v>
+        <v>0.3756</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8808</v>
+        <v>-0.3039</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2831</v>
+        <v>0.6795</v>
       </c>
       <c r="V19" t="n">
         <v>2.2224</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8991</v>
+        <v>1.2767</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7322</v>
+        <v>-0.329</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8332</v>
+        <v>1.6058</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9908</v>
+        <v>0.3249</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5091</v>
+        <v>0.2384</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0884</v>
+        <v>-0.0259</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5882</v>
+        <v>0.4644</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5003</v>
+        <v>-0.4902</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0976</v>
+        <v>0.3508</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0973</v>
+        <v>-0.2259</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0003</v>
+        <v>0.5768</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3823</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8428</v>
+        <v>0.1742</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7383</v>
+        <v>-0.3032</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1045</v>
+        <v>0.4774</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5681</v>
+        <v>-0.3219</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6543</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2224</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.758</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5213</v>
+        <v>-1.5247</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2794</v>
+        <v>1.6082</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3249</v>
+        <v>0.0743</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2384</v>
+        <v>-0.0507</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0259</v>
+        <v>-0.4293</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4644</v>
+        <v>0.0867</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4902</v>
+        <v>-0.516</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3508</v>
+        <v>0.5036</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2259</v>
+        <v>-0.1374</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5768</v>
+        <v>0.641</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3445</v>
+        <v>0.1925</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4955</v>
+        <v>-0.1791</v>
       </c>
       <c r="U21" t="n">
-        <v>0.151</v>
+        <v>0.3716</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2356</v>
+        <v>-0.3714</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6209</v>
+        <v>1.4822</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3853</v>
+        <v>-1.8536</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0743</v>
+        <v>0.9908</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0507</v>
+        <v>-0.5091</v>
       </c>
       <c r="I22" t="n">
-        <v>0.125</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4293</v>
+        <v>3.0884</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0867</v>
+        <v>1.5882</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.516</v>
+        <v>1.5003</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5036</v>
+        <v>-2.0976</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1374</v>
+        <v>-2.0973</v>
       </c>
       <c r="O22" t="n">
-        <v>0.641</v>
+        <v>-0.0003</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R22" t="n">
-        <v>0.733</v>
+        <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1266</v>
+        <v>0.5724</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2753</v>
+        <v>0.4883</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1486</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.5681</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6543</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5836</v>
+        <v>-3.094</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0285</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5551</v>
+        <v>-2.2578</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6709</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8289</v>
+        <v>-0.3394</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1297</v>
+        <v>0.0626</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6993</v>
+        <v>-0.402</v>
       </c>
       <c r="V23" t="n">
         <v>-1.267</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.266</v>
+        <v>-6.5633</v>
       </c>
       <c r="E24" t="n">
         <v>-4.6331</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6329</v>
+        <v>-1.9302</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7752</v>
@@ -2326,13 +2326,13 @@
         <v>2.9321</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4255</v>
+        <v>0.1282</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1493</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5748</v>
+        <v>0.2775</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.797600000000001</v>
+        <v>8.438600000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>10.1512</v>
+        <v>10.1514</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3536</v>
+        <v>-1.7125</v>
       </c>
       <c r="G25" t="n">
         <v>5.5573</v>
@@ -2374,7 +2374,7 @@
         <v>-4.3809</v>
       </c>
       <c r="I25" t="n">
-        <v>9.938199999999998</v>
+        <v>9.9382</v>
       </c>
       <c r="J25" t="n">
         <v>17.0686</v>
@@ -2404,13 +2404,13 @@
         <v>16.493</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6410999999999998</v>
+        <v>1.282</v>
       </c>
       <c r="T25" t="n">
         <v>-0.2902999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9311999999999998</v>
+        <v>1.5724</v>
       </c>
       <c r="V25" t="n">
         <v>1.5993</v>
